--- a/per-stock/KEYS/financials.xlsx
+++ b/per-stock/KEYS/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59171131392</v>
+        <v>62149517312</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59608760320</v>
+        <v>62500519936</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55.896774</v>
+        <v>58.46785</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.229881</v>
+        <v>30.672989</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.719305</v>
+        <v>10.208528</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.63666</v>
+        <v>0.62139</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -621,7 +630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.18055001</v>
+        <v>0.18812001</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2759000064</v>
+        <v>2763000064</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1143250048</v>
+        <v>1357000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>170738495</v>
+        <v>170895368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>346.56</v>
+        <v>363.67</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D41</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C41</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B41</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B40:E40)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D39</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C39</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B39</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B38:E38)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D34</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C34</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B34</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B33:E33)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D8</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C8</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B8</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B8:E8)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1609,13 +2089,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1624,7 +2104,6 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1658,11 +2137,6 @@
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1670,7 +2144,9 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
@@ -1683,9 +2159,6 @@
       <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1693,7 +2166,9 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="n">
+        <v>0.165072</v>
+      </c>
       <c r="C3" s="3" t="n">
         <v>0.4</v>
       </c>
@@ -1704,10 +2179,7 @@
         <v>0.208</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.15</v>
+        <v>0.196875</v>
       </c>
     </row>
     <row r="4">
@@ -1716,7 +2188,9 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="3" t="n">
+        <v>550000000</v>
+      </c>
       <c r="C4" s="3" t="n">
         <v>332000000</v>
       </c>
@@ -1729,9 +2203,6 @@
       <c r="F4" s="3" t="n">
         <v>408000000</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>285000000</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1739,7 +2210,9 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
+      <c r="B5" s="3" t="n">
+        <v>349000000</v>
+      </c>
       <c r="C5" s="3" t="n">
         <v>281000000</v>
       </c>
@@ -1752,9 +2225,6 @@
       <c r="F5" s="3" t="n">
         <v>257000000</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>169000000</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1762,7 +2232,9 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
+      <c r="B6" s="3" t="n">
+        <v>107000000</v>
+      </c>
       <c r="C6" s="3" t="n">
         <v>105000000</v>
       </c>
@@ -1775,9 +2247,6 @@
       <c r="F6" s="3" t="n">
         <v>68000000</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>66000000</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1785,7 +2254,9 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
+      <c r="B7" s="3" t="n">
+        <v>539000000</v>
+      </c>
       <c r="C7" s="3" t="n">
         <v>605000000</v>
       </c>
@@ -1798,9 +2269,6 @@
       <c r="F7" s="3" t="n">
         <v>492000000</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>478000000</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1808,7 +2276,9 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
+      <c r="B8" s="3" t="n">
+        <v>550000000</v>
+      </c>
       <c r="C8" s="3" t="n">
         <v>332000000</v>
       </c>
@@ -1821,9 +2291,6 @@
       <c r="F8" s="3" t="n">
         <v>408000000</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>285000000</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1831,7 +2298,9 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
+      <c r="B9" s="3" t="n">
+        <v>443000000</v>
+      </c>
       <c r="C9" s="3" t="n">
         <v>227000000</v>
       </c>
@@ -1844,9 +2313,6 @@
       <c r="F9" s="3" t="n">
         <v>340000000</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>219000000</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1854,7 +2320,9 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
+      <c r="B10" s="3" t="n">
+        <v>-7000000</v>
+      </c>
       <c r="C10" s="3" t="n">
         <v>-13000000</v>
       </c>
@@ -1867,9 +2335,6 @@
       <c r="F10" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>-1000000</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1877,7 +2342,9 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="3" t="n">
+        <v>25000000</v>
+      </c>
       <c r="C11" s="3" t="n">
         <v>29000000</v>
       </c>
@@ -1890,9 +2357,6 @@
       <c r="F11" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>20000000</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1900,7 +2364,9 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="3" t="n">
+        <v>18000000</v>
+      </c>
       <c r="C12" s="3" t="n">
         <v>16000000</v>
       </c>
@@ -1913,9 +2379,6 @@
       <c r="F12" s="3" t="n">
         <v>21000000</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>19000000</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1923,7 +2386,9 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="n">
+        <v>349000000</v>
+      </c>
       <c r="C13" s="3" t="n">
         <v>281000000</v>
       </c>
@@ -1936,9 +2401,6 @@
       <c r="F13" s="3" t="n">
         <v>257000000</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>169000000</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1946,7 +2408,9 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="n">
+        <v>349000000</v>
+      </c>
       <c r="C14" s="3" t="n">
         <v>281000000</v>
       </c>
@@ -1959,9 +2423,6 @@
       <c r="F14" s="3" t="n">
         <v>257000000</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>169000000</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1969,7 +2430,9 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="n">
+        <v>1310000000</v>
+      </c>
       <c r="C15" s="3" t="n">
         <v>1352000000</v>
       </c>
@@ -1982,9 +2445,6 @@
       <c r="F15" s="3" t="n">
         <v>1099000000</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>1080000000</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1992,7 +2452,9 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="3" t="n">
+        <v>407000000</v>
+      </c>
       <c r="C16" s="3" t="n">
         <v>248000000</v>
       </c>
@@ -2005,9 +2467,6 @@
       <c r="F16" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>218000000</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2030,7 +2489,6 @@
       <c r="F17" s="3" t="n">
         <v>173000000</v>
       </c>
-      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2053,7 +2511,6 @@
       <c r="F18" s="3" t="n">
         <v>172000000</v>
       </c>
-      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2076,7 +2533,6 @@
       <c r="F19" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2099,7 +2555,6 @@
       <c r="F20" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2107,7 +2562,9 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
+      <c r="B21" s="3" t="n">
+        <v>349000000</v>
+      </c>
       <c r="C21" s="3" t="n">
         <v>281000000</v>
       </c>
@@ -2120,9 +2577,6 @@
       <c r="F21" s="3" t="n">
         <v>257000000</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>169000000</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2130,7 +2584,9 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
+      <c r="B22" s="3" t="n">
+        <v>349000000</v>
+      </c>
       <c r="C22" s="3" t="n">
         <v>281000000</v>
       </c>
@@ -2143,9 +2599,6 @@
       <c r="F22" s="3" t="n">
         <v>257000000</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>169000000</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2153,7 +2606,9 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
+      <c r="B23" s="3" t="n">
+        <v>349000000</v>
+      </c>
       <c r="C23" s="3" t="n">
         <v>281000000</v>
       </c>
@@ -2166,9 +2621,6 @@
       <c r="F23" s="3" t="n">
         <v>257000000</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>169000000</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2176,7 +2628,9 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
+      <c r="B24" s="3" t="n">
+        <v>349000000</v>
+      </c>
       <c r="C24" s="3" t="n">
         <v>281000000</v>
       </c>
@@ -2189,9 +2643,6 @@
       <c r="F24" s="3" t="n">
         <v>257000000</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>169000000</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2199,7 +2650,9 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
+      <c r="B25" s="3" t="n">
+        <v>349000000</v>
+      </c>
       <c r="C25" s="3" t="n">
         <v>281000000</v>
       </c>
@@ -2212,9 +2665,6 @@
       <c r="F25" s="3" t="n">
         <v>257000000</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>169000000</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2222,7 +2672,9 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
+      <c r="B26" s="3" t="n">
+        <v>69000000</v>
+      </c>
       <c r="C26" s="3" t="n">
         <v>-83000000</v>
       </c>
@@ -2235,9 +2687,6 @@
       <c r="F26" s="3" t="n">
         <v>63000000</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>30000000</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2245,7 +2694,9 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
+      <c r="B27" s="3" t="n">
+        <v>418000000</v>
+      </c>
       <c r="C27" s="3" t="n">
         <v>198000000</v>
       </c>
@@ -2258,9 +2709,6 @@
       <c r="F27" s="3" t="n">
         <v>320000000</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>199000000</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2268,7 +2716,9 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
+      <c r="B28" s="3" t="n">
+        <v>18000000</v>
+      </c>
       <c r="C28" s="3" t="n">
         <v>-37000000</v>
       </c>
@@ -2281,9 +2731,6 @@
       <c r="F28" s="3" t="n">
         <v>112000000</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>-18000000</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2291,7 +2738,9 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
+      <c r="B29" s="3" t="n">
+        <v>18000000</v>
+      </c>
       <c r="C29" s="3" t="n">
         <v>-37000000</v>
       </c>
@@ -2304,9 +2753,6 @@
       <c r="F29" s="3" t="n">
         <v>112000000</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>-18000000</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2314,7 +2760,9 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
+      <c r="B30" s="3" t="n">
+        <v>-7000000</v>
+      </c>
       <c r="C30" s="3" t="n">
         <v>-13000000</v>
       </c>
@@ -2327,9 +2775,6 @@
       <c r="F30" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="G30" s="3" t="n">
-        <v>-1000000</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2337,7 +2782,9 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
+      <c r="B31" s="3" t="n">
+        <v>25000000</v>
+      </c>
       <c r="C31" s="3" t="n">
         <v>29000000</v>
       </c>
@@ -2350,9 +2797,6 @@
       <c r="F31" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>20000000</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2360,7 +2804,9 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
+      <c r="B32" s="3" t="n">
+        <v>18000000</v>
+      </c>
       <c r="C32" s="3" t="n">
         <v>16000000</v>
       </c>
@@ -2373,9 +2819,6 @@
       <c r="F32" s="3" t="n">
         <v>21000000</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>19000000</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2383,7 +2826,9 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
+      <c r="B33" s="3" t="n">
+        <v>407000000</v>
+      </c>
       <c r="C33" s="3" t="n">
         <v>248000000</v>
       </c>
@@ -2396,9 +2841,6 @@
       <c r="F33" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>218000000</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2406,7 +2848,9 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
+      <c r="B34" s="3" t="n">
+        <v>771000000</v>
+      </c>
       <c r="C34" s="3" t="n">
         <v>747000000</v>
       </c>
@@ -2419,9 +2863,6 @@
       <c r="F34" s="3" t="n">
         <v>607000000</v>
       </c>
-      <c r="G34" s="3" t="n">
-        <v>602000000</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2429,7 +2870,9 @@
           <t>Other Operating Expenses</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
+      <c r="B35" s="3" t="n">
+        <v>-5000000</v>
+      </c>
       <c r="C35" s="3" t="n">
         <v>-3000000</v>
       </c>
@@ -2442,9 +2885,6 @@
       <c r="F35" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>-8000000</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2452,7 +2892,9 @@
           <t>Research And Development</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
+      <c r="B36" s="3" t="n">
+        <v>320000000</v>
+      </c>
       <c r="C36" s="3" t="n">
         <v>303000000</v>
       </c>
@@ -2465,9 +2907,6 @@
       <c r="F36" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>249000000</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2475,7 +2914,9 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
+      <c r="B37" s="3" t="n">
+        <v>456000000</v>
+      </c>
       <c r="C37" s="3" t="n">
         <v>447000000</v>
       </c>
@@ -2488,9 +2929,6 @@
       <c r="F37" s="3" t="n">
         <v>360000000</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>361000000</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2498,7 +2936,9 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
+      <c r="B38" s="3" t="n">
+        <v>1178000000</v>
+      </c>
       <c r="C38" s="3" t="n">
         <v>995000000</v>
       </c>
@@ -2511,9 +2951,6 @@
       <c r="F38" s="3" t="n">
         <v>814000000</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>820000000</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2521,7 +2958,9 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
+      <c r="B39" s="3" t="n">
+        <v>539000000</v>
+      </c>
       <c r="C39" s="3" t="n">
         <v>605000000</v>
       </c>
@@ -2534,9 +2973,6 @@
       <c r="F39" s="3" t="n">
         <v>492000000</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>478000000</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2544,7 +2980,9 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n"/>
+      <c r="B40" s="3" t="n">
+        <v>1717000000</v>
+      </c>
       <c r="C40" s="3" t="n">
         <v>1600000000</v>
       </c>
@@ -2557,9 +2995,6 @@
       <c r="F40" s="3" t="n">
         <v>1306000000</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>1298000000</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2567,7 +3002,9 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
+      <c r="B41" s="3" t="n">
+        <v>1717000000</v>
+      </c>
       <c r="C41" s="3" t="n">
         <v>1600000000</v>
       </c>
@@ -2579,9 +3016,6 @@
       </c>
       <c r="F41" s="3" t="n">
         <v>1306000000</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>1298000000</v>
       </c>
     </row>
   </sheetData>
@@ -2589,7 +3023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4087,7 +4521,1885 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>31236000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>30813000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>29914000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>170738495</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>171394127</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>171267000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>171874000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>171790000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>202738495</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>202630127</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>202080000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>202074000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>201704000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>356000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>661000000</v>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2759000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2772000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2778000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2764000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2765000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1692000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1480000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1153000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2717000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2488000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>8862000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>8739000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>8415000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8203000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>8009000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2393000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2896000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2498000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>4044000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>3852000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1692000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1480000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1153000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2717000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2488000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>228000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>238000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>231000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>233000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>6331000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>6205000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>5881000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>5670000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>5477000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>8163000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>8739000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>8415000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>8203000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>8009000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>6331000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>6205000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>5881000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>5670000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>5477000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>6331000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>6205000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>5881000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>5670000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>5477000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-250000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-199000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-248000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-295000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-293000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-250000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-199000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-248000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-295000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-293000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>4108000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>3886000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>3799000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>3698000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>3648000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>7705000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>7356000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>7075000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>6842000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>6651000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2982000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>2932000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2851000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2819000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2765000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5407000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>5276000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>5420000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>4981000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>5058000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>2758000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>3471000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>3570000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>3421000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>3444000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>423000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>439000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>536000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>413000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>425000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>76000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>82000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>76000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>82000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>251000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>237000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>232000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>251000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>237000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>232000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>2008000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>2720000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>2727000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>2716000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2719000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>176000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>186000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>193000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>183000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>187000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1832000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>2534000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>2534000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>2533000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2532000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>2649000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1805000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1850000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>1560000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1614000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>737000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>729000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>652000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>557000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>612000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>737000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>729000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>652000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>557000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>612000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>751000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>699000000</v>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>699000000</v>
+      </c>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>448000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>329000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>399000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>290000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>319000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>713000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>695000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>748000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>665000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>637000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>197000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>186000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>179000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>145000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>516000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>530000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>562000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>486000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>492000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>124000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>196000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>207000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>144000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>175000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>392000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>334000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>355000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>342000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>317000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>11738000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>11481000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>11301000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>10651000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>10535000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>6696000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>6780000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>6953000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>5047000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>5069000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>592000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>592000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>91000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>555000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>568000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Defined Pension Benefit</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="n">
+        <v>408000000</v>
+      </c>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n">
+        <v>324000000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>335000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>330000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>373000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>392000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>379000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>335000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>330000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>373000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>392000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>379000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Non Current Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
+        <v>111000000</v>
+      </c>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n">
+        <v>111000000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>169000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>147000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>211000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>157000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>4639000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>4725000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>4728000000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>2953000000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>2989000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>1174000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1251000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1304000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>524000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>556000000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>3465000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>3474000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>3424000000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>2429000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>2433000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>961000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>986000000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1031000000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>990000000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>995000000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>-1804000000</v>
+      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n">
+        <v>-1706000000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>961000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>986000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>2835000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>990000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>995000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>961000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>986000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>236000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>990000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>995000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" s="3" t="n">
+        <v>1672000000</v>
+      </c>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n">
+        <v>1581000000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n">
+        <v>879000000</v>
+      </c>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n">
+        <v>851000000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n">
+        <v>48000000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>5042000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>4701000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>4348000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>5604000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>5466000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>199000000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>175000000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>166000000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>192000000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>163000000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n">
+        <v>759000000</v>
+      </c>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>271000000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>273000000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>285000000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>304000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>303000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>1038000000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1048000000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>1021000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>1026000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>421000000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>435000000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>425000000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>393000000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>388000000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>617000000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>613000000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>625000000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>628000000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>638000000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>1122000000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>1027000000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>974000000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>692000000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>856000000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>113000000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n">
+        <v>112000000</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>144000000</v>
+      </c>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>1022000000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>914000000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>939000000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>692000000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>744000000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n">
+        <v>-12000000</v>
+      </c>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n">
+        <v>-9000000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
+      <c r="D78" s="3" t="n">
+        <v>951000000</v>
+      </c>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n">
+        <v>866000000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>2412000000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>2178000000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>1873000000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>2636000000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>3118000000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>2412000000</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>2178000000</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>1873000000</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>2636000000</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>3118000000</v>
+      </c>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5307,13 +7619,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5323,6 +7635,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5333,30 +7646,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5369,21 +7687,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>472000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>407000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>187000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>291000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>457000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>346000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5392,21 +7711,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-223000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-87000000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-99000000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-153000000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-75000000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5415,15 +7735,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="n"/>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n">
         <v>-600000000</v>
       </c>
     </row>
@@ -5434,15 +7755,16 @@
         </is>
       </c>
       <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="n"/>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5451,21 +7773,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-29000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-34000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-38000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-31000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-27000000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-32000000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5474,21 +7797,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>32000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>38000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>39000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5497,21 +7821,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>18000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>46000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>30000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>35000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>9000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5520,21 +7845,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>2430000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>2195000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>1890000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>3397000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>3135000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>2077000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5543,21 +7869,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>2195000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1890000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>3397000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>3135000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>2077000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>1814000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5566,21 +7893,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>18000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-8000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5589,21 +7917,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>236000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>298000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-1507000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>263000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>1040000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>271000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5612,21 +7941,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-229000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-99000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-102000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-28000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>589000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-74000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5635,21 +7965,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-229000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-99000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-102000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-28000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>589000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-74000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5658,21 +7989,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-44000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-10000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-6000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-30000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5681,21 +8013,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>32000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>32000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>31000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5704,21 +8037,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-223000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-87000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-99000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-153000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-75000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5727,21 +8061,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-223000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-87000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-99000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-153000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-75000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5750,15 +8085,16 @@
         </is>
       </c>
       <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="n"/>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
         <v>-1000000</v>
       </c>
     </row>
@@ -5769,15 +8105,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="n"/>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
         <v>-1000000</v>
       </c>
     </row>
@@ -5788,15 +8125,16 @@
         </is>
       </c>
       <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="n"/>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n">
         <v>-600000000</v>
       </c>
     </row>
@@ -5807,15 +8145,16 @@
         </is>
       </c>
       <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="n"/>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5824,21 +8163,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-36000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-44000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-1630000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-31000000</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>-33000000</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-33000000</v>
       </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5847,21 +8187,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-36000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-44000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-1630000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-31000000</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-33000000</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>-33000000</v>
       </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5869,22 +8210,23 @@
           <t>Net Other Investing Changes</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-2000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="G25" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5893,15 +8235,20 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-7000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="G26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5910,15 +8257,20 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="3" t="n"/>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5927,21 +8279,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-16000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-1620000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5950,21 +8303,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-16000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-2019000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5973,21 +8327,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-29000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-34000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-38000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-31000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-27000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-32000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5996,21 +8351,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-29000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-34000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-38000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-31000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-27000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-32000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6019,21 +8375,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>501000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>441000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>225000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>322000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>484000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>378000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6042,21 +8399,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>501000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>441000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>225000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>322000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>484000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>378000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6065,21 +8423,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-83000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>56000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>125000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>118000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6088,21 +8447,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-6000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>69000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-77000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>78000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6111,21 +8471,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-54000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>60000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>45000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>18000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6134,21 +8495,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-54000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>60000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>45000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>18000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6157,21 +8519,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>59000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>-13000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>22000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>23000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-16000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6180,21 +8543,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-62000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-41000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>63000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-14000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>22000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>34000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6203,21 +8567,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-62000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-41000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>63000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-14000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>22000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>34000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6230,7 +8595,8 @@
       <c r="D41" s="3" t="n"/>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n">
         <v>39000000</v>
       </c>
     </row>
@@ -6250,12 +8616,13 @@
         <v>-3000000</v>
       </c>
       <c r="E42" s="3" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-26000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6264,21 +8631,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-69000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>-123000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>128000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>75000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>48000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6287,21 +8655,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>-122000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>33000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-150000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>50000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>70000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>53000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6310,21 +8679,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>15000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>14000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>11000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>14000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>10000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6333,21 +8703,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>76000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>33000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>36000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>62000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6356,15 +8727,20 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>-5000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>53000000</v>
       </c>
-      <c r="C47" s="3" t="n"/>
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="G47" s="3" t="n">
         <v>-37000000</v>
       </c>
-      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6373,21 +8749,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>-29000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>-58000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>-18000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>-30000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>-10000000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6396,21 +8773,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-29000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>-58000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>-18000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>-30000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>-10000000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6419,21 +8797,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>107000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>105000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>75000000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>68000000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>66000000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6442,21 +8821,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>107000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>105000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>75000000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>68000000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>66000000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6465,21 +8845,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>41000000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>34000000</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>35000000</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>35000000</v>
       </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6488,21 +8869,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>41000000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>34000000</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>35000000</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>35000000</v>
       </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6511,21 +8893,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>38000000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>34000000</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>33000000</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>33000000</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>31000000</v>
+        <v>33000000</v>
       </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6534,21 +8917,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>18000000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>-16000000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>14000000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>-37000000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6558,16 +8942,17 @@
       </c>
       <c r="B56" s="3" t="n"/>
       <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n">
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n">
         <v>-16000000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>14000000</v>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="G56" s="3" t="n">
         <v>-37000000</v>
       </c>
-      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6576,13 +8961,16 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="C57" s="3" t="n"/>
       <c r="D57" s="3" t="n"/>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6591,28 +8979,29 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>349000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>281000000</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>233000000</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>191000000</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="F58" s="3" t="n">
         <v>257000000</v>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>169000000</v>
-      </c>
       <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
